--- a/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-14557_Datatype_Constructor_New_Operator_Vocabulary_Validation.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-14557_Datatype_Constructor_New_Operator_Vocabulary_Validation.xlsx
@@ -2,11 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView activeTab="0"/>
+  </bookViews>
   <sheets>
     <sheet state="visible" name="Rules" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="Type" sheetId="2" r:id="rId5"/>
   </sheets>
-  <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -17,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="41">
   <si>
     <t>Datatype Gender &lt;String&gt;</t>
   </si>
@@ -149,11 +151,40 @@
   <si>
     <t>check19</t>
   </si>
+  <si>
+    <t>Datatype Country &lt;String&gt;</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>NJ</t>
+  </si>
+  <si>
+    <t>= new MyDataType(
+    "Male",
+    "FMale",
+    "F3",
+    100,
+    999,
+    "AB",
+    new String[] {"CA", "NY","NJ"},
+    new String[] {"NJ" , "NY"},
+    "Female",
+    200,
+    300,
+    null,
+    null,
+    33,
+    new Level[] { 44 }
+)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
       <sz val="11.0"/>
@@ -162,13 +193,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color theme="1"/>
+      <color theme="1" rgb="000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
-      <color theme="1"/>
+      <color theme="1" rgb="000000"/>
       <name val="Calibri"/>
     </font>
     <font/>
@@ -221,7 +252,7 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1" xfId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -452,12 +483,13 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B1:C1005"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.71"/>
-    <col customWidth="1" min="2" max="2" width="34.0"/>
-    <col customWidth="1" min="3" max="3" width="31.57"/>
-    <col customWidth="1" min="4" max="26" width="8.71"/>
+    <col min="1" max="1" customWidth="true" width="8.71"/>
+    <col min="2" max="2" customWidth="true" width="34.0"/>
+    <col min="3" max="3" customWidth="true" width="31.57"/>
+    <col min="4" max="26" customWidth="true" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,21 +527,9 @@
         <v>300.0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
     <row r="14">
       <c r="B14" s="1" t="s">
         <v>7</v>
@@ -528,7 +548,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -1521,6 +1541,26 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1002">
+      <c r="B1002" t="s" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="B1003" t="s" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="B1004" t="s" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="B1005" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
@@ -1534,9 +1574,10 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:C1000"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="8.71"/>
+    <col min="1" max="26" customWidth="true" width="8.71"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -1594,109 +1635,81 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>22</v>
+      <c r="B9" t="s" s="6">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s" s="6">
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="B21" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="6" t="s">
         <v>36</v>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
